--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6219-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6219-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9B5EB1E-389C-41B3-85D0-6BAA111DCF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C97EE95B-3CDD-406A-AA4F-B363392DD513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{57235671-2EFC-45AA-BDB6-015254844DB3}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{456FF626-4286-472B-A517-C1176CF49BAA}"/>
   </bookViews>
   <sheets>
     <sheet name="6219-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1562,25 +1562,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE14673C-949B-440F-94BA-1475A1FCF4B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E348097-BD0C-4BAE-A1FD-C866C2FB8DDB}">
   <dimension ref="A1:R65"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.77734375" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1734,7 +1734,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>2025</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="43" t="s">
         <v>25</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
       <c r="B11" s="22" t="s">
         <v>31</v>
@@ -2088,7 +2088,7 @@
       <c r="Q11" s="48"/>
       <c r="R11" s="48"/>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2024</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>2023</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2022</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2021</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>25</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="s">
         <v>25</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>8.32</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>25</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2020</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>25</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>25</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>25</v>
       </c>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>25</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="41">
         <v>2019</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>25</v>
       </c>
@@ -3924,7 +3924,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>25</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>25</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39">
         <v>2018</v>
       </c>
@@ -4090,7 +4090,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>2017</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="39">
         <v>2016</v>
       </c>
@@ -4198,7 +4198,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>2015</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="39">
         <v>2014</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>2013</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="39">
         <v>2012</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>2011</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="39">
         <v>2010</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>2009</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="39">
         <v>2008</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>2007</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="39">
         <v>2006</v>
       </c>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="41">
         <v>2005</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="39">
         <v>2004</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="41">
         <v>2003</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="63" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="39">
         <v>2002</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="41">
         <v>2001</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="39" t="s">
         <v>60</v>
       </c>
